--- a/assets/docs/Ashraellen_Budget_2026_RU.xlsx
+++ b/assets/docs/Ashraellen_Budget_2026_RU.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R82733c3bcfc04583"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подробный бюджет" sheetId="2" r:id="R20bf06f5a59245aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сценарии" sheetId="3" r:id="R401c79f8b0fa45bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Производственные допущения" sheetId="4" r:id="R9c18f0cdac75406d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="5" r:id="R07216b9f28e1493b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R389613bf3a3645d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подробный бюджет" sheetId="2" r:id="R0cd4f08127b24071"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сценарии" sheetId="3" r:id="R616bd6b6e1c84605"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Производственные допущения" sheetId="4" r:id="R7fdda94c09b54c19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="5" r:id="R24cb00fb87804f5b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,13 +17,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="6">
     <x:numFmt numFmtId="200" formatCode="#,##0 €"/>
     <x:numFmt numFmtId="201" formatCode="0.0%"/>
     <x:numFmt numFmtId="202" formatCode="0.00"/>
     <x:numFmt numFmtId="203" formatCode="#,##0"/>
+    <x:numFmt numFmtId="204" formatCode="0"/>
+    <x:numFmt numFmtId="205" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="6">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -57,8 +59,13 @@
       <x:color rgb="111827"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -85,6 +92,11 @@
         <x:fgColor rgb="FEF3C7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="E6F2FF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="20">
     <x:border/>
@@ -345,7 +357,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="72">
+  <x:cellXfs count="77">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -484,6 +496,15 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="203" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -682,7 +703,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>Годовой бюджет многоязычной литературно-медийной исследовательской платформы</x:v>
+        <x:v>Годовой бюджет многоязычной художественно-философской исследовательской платформы</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str"/>
       <x:c r="C2" s="11" t="str"/>
@@ -692,7 +713,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="17" t="str">
-        <x:v>Основной рабочий сценарий на двенадцать месяцев устойчивой работы: письмо, исследование, публикации, перевод, видео/аудиопроизводство и развитие платформы.</x:v>
+        <x:v>Основной рабочий сценарий на двенадцать месяцев устойчивого художественного исследования, письма, редактирования, публикации, перевода, видео/аудиоформ и развития платформы. Инфраструктура служит исследованию, а не наоборот.</x:v>
       </x:c>
       <x:c r="B4" s="17"/>
       <x:c r="C4" s="17"/>
@@ -724,7 +745,7 @@
         <x:v>Поддержка жизни</x:v>
       </x:c>
       <x:c r="B8" s="44" t="str">
-        <x:v>Базовая поддержка жизни, необходимая для высвобождения устойчивого рабочего времени для письма, исследования, редактирования и развития платформы.</x:v>
+        <x:v>Базовая поддержка жизни, необходимая для высвобождения устойчивого рабочего времени для художественно-философского исследования, письма, редактирования и развития платформы.</x:v>
       </x:c>
       <x:c r="C8" s="45" t="n">
         <x:v>24000</x:v>
@@ -735,7 +756,7 @@
         <x:v>Цифровые инструменты и AI-производство</x:v>
       </x:c>
       <x:c r="B9" s="44" t="str">
-        <x:v>Google AI Ultra, ElevenLabs Business, ChatGPT/Codex-assisted development, монтажные/SEO-инструменты и технические подписки.</x:v>
+        <x:v>AI, голос, код, перевод, монтажные и технические инструменты как инфраструктура фиксации и передачи исследования в разных языках и форматах.</x:v>
       </x:c>
       <x:c r="C9" s="45" t="n">
         <x:v>17004</x:v>
@@ -746,7 +767,7 @@
         <x:v>Видео-шаблоны и рендер-инфраструктура</x:v>
       </x:c>
       <x:c r="B10" s="44" t="str">
-        <x:v>Многоразовые шаблоны Remotion, локальный рендер, тестирование и небольшой резерв на рендер/облако.</x:v>
+        <x:v>Многоразовые шаблоны Remotion, локальный рендер, тестирование и небольшой резерв на рендер/облако для регулярных публичных форм исследования.</x:v>
       </x:c>
       <x:c r="C10" s="45" t="n">
         <x:v>600</x:v>
@@ -757,7 +778,7 @@
         <x:v>Оборудование / рабочая станция</x:v>
       </x:c>
       <x:c r="B11" s="44" t="str">
-        <x:v>Мощный ноутбук/рабочая станция, широкий монитор, внешний SSD/резервный диск, хаб/периферия для видео и публикаций.</x:v>
+        <x:v>Мощный ноутбук/рабочая станция, широкий монитор, внешний SSD/резервный диск, хаб/периферия для редактирования, публикации и работы с многоязычным архивом.</x:v>
       </x:c>
       <x:c r="C11" s="45" t="n">
         <x:v>6000</x:v>
@@ -768,7 +789,7 @@
         <x:v>Интернет, резервное копирование и технический резерв</x:v>
       </x:c>
       <x:c r="B12" s="44" t="str">
-        <x:v>Стабильное подключение, мобильный/дорожный интернет-резерв, бэкапы, запас хранилища и техническая непрерывность.</x:v>
+        <x:v>Стабильное подключение, мобильный/дорожный интернет-резерв, бэкапы, запас хранилища и техническая непрерывность для сохранения архива и рабочих материалов.</x:v>
       </x:c>
       <x:c r="C12" s="45" t="n">
         <x:v>2000</x:v>
@@ -814,7 +835,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d293665d36f41d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87b6c144bb984273"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -841,7 +862,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>Годовой бюджет многоязычной литературно-медийной исследовательской платформы</x:v>
+        <x:v>Годовой бюджет многоязычной художественно-философской исследовательской платформы</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str"/>
       <x:c r="C2" s="11" t="str"/>
@@ -868,7 +889,7 @@
         <x:v>Поддержка жизни</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>Базовая поддержка жизни, необходимая для высвобождения устойчивого рабочего времени для письма, исследования, редактирования и развития платформы.</x:v>
+        <x:v>Базовая поддержка жизни, необходимая для высвобождения устойчивого рабочего времени для художественно-философского исследования, письма, редактирования и развития платформы.</x:v>
       </x:c>
       <x:c r="C5" s="28" t="n">
         <x:v>24000</x:v>
@@ -883,7 +904,7 @@
         <x:v>Цифровые инструменты и AI-производство</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>Google AI Ultra, ElevenLabs Business, ChatGPT/Codex-assisted development, монтажные/SEO-инструменты и технические подписки.</x:v>
+        <x:v>AI, голос, код, перевод, монтажные и технические инструменты как инфраструктура фиксации и передачи исследования в разных языках и форматах.</x:v>
       </x:c>
       <x:c r="C6" s="28" t="n">
         <x:v>17004</x:v>
@@ -898,7 +919,7 @@
         <x:v>Видео-шаблоны и рендер-инфраструктура</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>Многоразовые шаблоны Remotion, локальный рендер, тестирование и небольшой резерв на рендер/облако.</x:v>
+        <x:v>Многоразовые шаблоны Remotion, локальный рендер, тестирование и небольшой резерв на рендер/облако для регулярных публичных форм исследования.</x:v>
       </x:c>
       <x:c r="C7" s="28" t="n">
         <x:v>600</x:v>
@@ -913,7 +934,7 @@
         <x:v>Оборудование / рабочая станция</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>Мощный ноутбук/рабочая станция, широкий монитор, внешний SSD/резервный диск, хаб/периферия для видео и публикаций.</x:v>
+        <x:v>Мощный ноутбук/рабочая станция, широкий монитор, внешний SSD/резервный диск, хаб/периферия для редактирования, публикации и работы с многоязычным архивом.</x:v>
       </x:c>
       <x:c r="C8" s="28" t="n">
         <x:v>6000</x:v>
@@ -928,7 +949,7 @@
         <x:v>Интернет, резервное копирование и технический резерв</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>Стабильное подключение, мобильный/дорожный интернет-резерв, бэкапы, запас хранилища и техническая непрерывность.</x:v>
+        <x:v>Стабильное подключение, мобильный/дорожный интернет-резерв, бэкапы, запас хранилища и техническая непрерывность для сохранения архива и рабочих материалов.</x:v>
       </x:c>
       <x:c r="C9" s="28" t="n">
         <x:v>2000</x:v>
@@ -989,7 +1010,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra68451b53d2644ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racef4359a1044e80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1188,7 +1209,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>Допущения по озвучке, видео и многоязычному производству</x:v>
+        <x:v>Допущения по озвучке, видео и многоязычному производству публичных форм исследования</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str"/>
       <x:c r="C2" s="11" t="str"/>
@@ -1244,7 +1265,7 @@
       <x:c r="A8" s="11" t="str">
         <x:v>Минут озвучки больших роликов в месяц</x:v>
       </x:c>
-      <x:c r="B8" s="68" t="n">
+      <x:c r="B8" s="75" t="n">
         <x:f>B5*B6*B7</x:f>
         <x:v>1890</x:v>
       </x:c>
@@ -1256,7 +1277,7 @@
       <x:c r="A9" s="11" t="str">
         <x:v>Shorts Saint Whine в месяц</x:v>
       </x:c>
-      <x:c r="B9" s="68" t="n">
+      <x:c r="B9" s="75" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
@@ -1267,7 +1288,7 @@
       <x:c r="A10" s="11" t="str">
         <x:v>Средняя длительность Short (минуты)</x:v>
       </x:c>
-      <x:c r="B10" s="68" t="n">
+      <x:c r="B10" s="75" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
@@ -1278,7 +1299,7 @@
       <x:c r="A11" s="11" t="str">
         <x:v>Языков для Shorts в базовом сценарии</x:v>
       </x:c>
-      <x:c r="B11" s="68" t="n">
+      <x:c r="B11" s="75" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
@@ -1289,7 +1310,7 @@
       <x:c r="A12" s="11" t="str">
         <x:v>Минут озвучки Shorts в месяц</x:v>
       </x:c>
-      <x:c r="B12" s="68" t="n">
+      <x:c r="B12" s="75" t="n">
         <x:f>B9*B10*B11</x:f>
         <x:v>30</x:v>
       </x:c>
@@ -1301,7 +1322,7 @@
       <x:c r="A13" s="11" t="str">
         <x:v>Резерв на перегенерации и тесты</x:v>
       </x:c>
-      <x:c r="B13" s="69" t="n">
+      <x:c r="B13" s="76" t="n">
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
@@ -1312,19 +1333,19 @@
       <x:c r="A14" s="11" t="str">
         <x:v>Оценка минут озвучки с резервом</x:v>
       </x:c>
-      <x:c r="B14" s="69" t="n">
+      <x:c r="B14" s="75" t="n">
         <x:f>(B8+B12)*(1+B13)</x:f>
         <x:v>2304</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>Большие ролики + Shorts + 20% резерв</x:v>
+        <x:v>(1 890 + 30) × 1,2 = 2 304 минут/месяц</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
         <x:v>Примерная месячная ёмкость ElevenLabs Business</x:v>
       </x:c>
-      <x:c r="B15" s="69" t="n">
+      <x:c r="B15" s="75" t="n">
         <x:v>6000</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
@@ -1335,13 +1356,34 @@
       <x:c r="A16" s="11" t="str">
         <x:v>Оценка запаса месячной ёмкости</x:v>
       </x:c>
-      <x:c r="B16" s="69" t="n">
+      <x:c r="B16" s="75" t="n">
         <x:f>B15-B14</x:f>
         <x:v>3696</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
         <x:v>Примерный запас на тесты, дополнительные Shorts и рост</x:v>
       </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="74" t="str">
+        <x:v>Иерархия бюджета</x:v>
+      </x:c>
+      <x:c r="B18" s="74"/>
+      <x:c r="C18" s="74"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="11" t="str">
+        <x:v>способ видеть → исследование смысла → формы фиксации → публичная платформа → производственная инфраструктура</x:v>
+      </x:c>
+      <x:c r="B19" s="11"/>
+      <x:c r="C19" s="11"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="11" t="str">
+        <x:v>Инфраструктура служит исследованию. Бюджет — не список технических хотелок, а рабочая база для сохранения, перевода и передачи исследования.</x:v>
+      </x:c>
+      <x:c r="B20" s="11"/>
+      <x:c r="C20" s="11"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/assets/docs/Ashraellen_Budget_2026_RU.xlsx
+++ b/assets/docs/Ashraellen_Budget_2026_RU.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R389613bf3a3645d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подробный бюджет" sheetId="2" r:id="R0cd4f08127b24071"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сценарии" sheetId="3" r:id="R616bd6b6e1c84605"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Производственные допущения" sheetId="4" r:id="R7fdda94c09b54c19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="5" r:id="R24cb00fb87804f5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="Rffca5d81e83f4876"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подробный бюджет" sheetId="2" r:id="R5df4870aa20b4f22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сценарии" sheetId="3" r:id="R6ed5bf7fd9cc4ffe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Производственные допущения" sheetId="4" r:id="Ra151ef37a0914948"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="5" r:id="R1eb96686cbdc40b2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -713,7 +713,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="17" t="str">
-        <x:v>Основной рабочий сценарий на двенадцать месяцев устойчивого художественного исследования, письма, редактирования, публикации, перевода, видео/аудиоформ и развития платформы. Инфраструктура служит исследованию, а не наоборот.</x:v>
+        <x:v>Основной рабочий сценарий на двенадцать месяцев устойчивого художественного исследования, письма, редактирования, публикации, перевода, видео/аудиоформ и развития платформы. Запрашиваемая инфраструктура является рабочей базой для сохранения, перевода и передачи исследования.</x:v>
       </x:c>
       <x:c r="B4" s="17"/>
       <x:c r="C4" s="17"/>
@@ -835,7 +835,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87b6c144bb984273"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d4ad21294e94518"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1010,7 +1010,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racef4359a1044e80"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06b614c014f044dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1380,7 +1380,7 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="str">
-        <x:v>Инфраструктура служит исследованию. Бюджет — не список технических хотелок, а рабочая база для сохранения, перевода и передачи исследования.</x:v>
+        <x:v>Инфраструктура является рабочей базой для сохранения, перевода и передачи исследования в литературных, аудио-, видео- и многоязычных форматах.</x:v>
       </x:c>
       <x:c r="B20" s="11"/>
       <x:c r="C20" s="11"/>

--- a/assets/docs/Ashraellen_Budget_2026_RU.xlsx
+++ b/assets/docs/Ashraellen_Budget_2026_RU.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="Rffca5d81e83f4876"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подробный бюджет" sheetId="2" r:id="R5df4870aa20b4f22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сценарии" sheetId="3" r:id="R6ed5bf7fd9cc4ffe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Производственные допущения" sheetId="4" r:id="Ra151ef37a0914948"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="5" r:id="R1eb96686cbdc40b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R82733c3bcfc04583"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подробный бюджет" sheetId="2" r:id="R20bf06f5a59245aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сценарии" sheetId="3" r:id="R401c79f8b0fa45bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Производственные допущения" sheetId="4" r:id="R9c18f0cdac75406d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="5" r:id="R07216b9f28e1493b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,15 +17,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="#,##0 €"/>
     <x:numFmt numFmtId="201" formatCode="0.0%"/>
     <x:numFmt numFmtId="202" formatCode="0.00"/>
     <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0"/>
-    <x:numFmt numFmtId="205" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="7">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -59,13 +57,8 @@
       <x:color rgb="111827"/>
       <x:name val="Carlito"/>
     </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:name val="Carlito"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -92,11 +85,6 @@
         <x:fgColor rgb="FEF3C7"/>
       </x:patternFill>
     </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="E6F2FF"/>
-      </x:patternFill>
-    </x:fill>
   </x:fills>
   <x:borders count="20">
     <x:border/>
@@ -357,7 +345,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="77">
+  <x:cellXfs count="72">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -496,15 +484,6 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="203" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="205" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -703,7 +682,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>Годовой бюджет многоязычной художественно-философской исследовательской платформы</x:v>
+        <x:v>Годовой бюджет многоязычной литературно-медийной исследовательской платформы</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str"/>
       <x:c r="C2" s="11" t="str"/>
@@ -713,7 +692,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="17" t="str">
-        <x:v>Основной рабочий сценарий на двенадцать месяцев устойчивого художественного исследования, письма, редактирования, публикации, перевода, видео/аудиоформ и развития платформы. Запрашиваемая инфраструктура является рабочей базой для сохранения, перевода и передачи исследования.</x:v>
+        <x:v>Основной рабочий сценарий на двенадцать месяцев устойчивой работы: письмо, исследование, публикации, перевод, видео/аудиопроизводство и развитие платформы.</x:v>
       </x:c>
       <x:c r="B4" s="17"/>
       <x:c r="C4" s="17"/>
@@ -745,7 +724,7 @@
         <x:v>Поддержка жизни</x:v>
       </x:c>
       <x:c r="B8" s="44" t="str">
-        <x:v>Базовая поддержка жизни, необходимая для высвобождения устойчивого рабочего времени для художественно-философского исследования, письма, редактирования и развития платформы.</x:v>
+        <x:v>Базовая поддержка жизни, необходимая для высвобождения устойчивого рабочего времени для письма, исследования, редактирования и развития платформы.</x:v>
       </x:c>
       <x:c r="C8" s="45" t="n">
         <x:v>24000</x:v>
@@ -756,7 +735,7 @@
         <x:v>Цифровые инструменты и AI-производство</x:v>
       </x:c>
       <x:c r="B9" s="44" t="str">
-        <x:v>AI, голос, код, перевод, монтажные и технические инструменты как инфраструктура фиксации и передачи исследования в разных языках и форматах.</x:v>
+        <x:v>Google AI Ultra, ElevenLabs Business, ChatGPT/Codex-assisted development, монтажные/SEO-инструменты и технические подписки.</x:v>
       </x:c>
       <x:c r="C9" s="45" t="n">
         <x:v>17004</x:v>
@@ -767,7 +746,7 @@
         <x:v>Видео-шаблоны и рендер-инфраструктура</x:v>
       </x:c>
       <x:c r="B10" s="44" t="str">
-        <x:v>Многоразовые шаблоны Remotion, локальный рендер, тестирование и небольшой резерв на рендер/облако для регулярных публичных форм исследования.</x:v>
+        <x:v>Многоразовые шаблоны Remotion, локальный рендер, тестирование и небольшой резерв на рендер/облако.</x:v>
       </x:c>
       <x:c r="C10" s="45" t="n">
         <x:v>600</x:v>
@@ -778,7 +757,7 @@
         <x:v>Оборудование / рабочая станция</x:v>
       </x:c>
       <x:c r="B11" s="44" t="str">
-        <x:v>Мощный ноутбук/рабочая станция, широкий монитор, внешний SSD/резервный диск, хаб/периферия для редактирования, публикации и работы с многоязычным архивом.</x:v>
+        <x:v>Мощный ноутбук/рабочая станция, широкий монитор, внешний SSD/резервный диск, хаб/периферия для видео и публикаций.</x:v>
       </x:c>
       <x:c r="C11" s="45" t="n">
         <x:v>6000</x:v>
@@ -789,7 +768,7 @@
         <x:v>Интернет, резервное копирование и технический резерв</x:v>
       </x:c>
       <x:c r="B12" s="44" t="str">
-        <x:v>Стабильное подключение, мобильный/дорожный интернет-резерв, бэкапы, запас хранилища и техническая непрерывность для сохранения архива и рабочих материалов.</x:v>
+        <x:v>Стабильное подключение, мобильный/дорожный интернет-резерв, бэкапы, запас хранилища и техническая непрерывность.</x:v>
       </x:c>
       <x:c r="C12" s="45" t="n">
         <x:v>2000</x:v>
@@ -835,7 +814,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d4ad21294e94518"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d293665d36f41d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -862,7 +841,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>Годовой бюджет многоязычной художественно-философской исследовательской платформы</x:v>
+        <x:v>Годовой бюджет многоязычной литературно-медийной исследовательской платформы</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str"/>
       <x:c r="C2" s="11" t="str"/>
@@ -889,7 +868,7 @@
         <x:v>Поддержка жизни</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>Базовая поддержка жизни, необходимая для высвобождения устойчивого рабочего времени для художественно-философского исследования, письма, редактирования и развития платформы.</x:v>
+        <x:v>Базовая поддержка жизни, необходимая для высвобождения устойчивого рабочего времени для письма, исследования, редактирования и развития платформы.</x:v>
       </x:c>
       <x:c r="C5" s="28" t="n">
         <x:v>24000</x:v>
@@ -904,7 +883,7 @@
         <x:v>Цифровые инструменты и AI-производство</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>AI, голос, код, перевод, монтажные и технические инструменты как инфраструктура фиксации и передачи исследования в разных языках и форматах.</x:v>
+        <x:v>Google AI Ultra, ElevenLabs Business, ChatGPT/Codex-assisted development, монтажные/SEO-инструменты и технические подписки.</x:v>
       </x:c>
       <x:c r="C6" s="28" t="n">
         <x:v>17004</x:v>
@@ -919,7 +898,7 @@
         <x:v>Видео-шаблоны и рендер-инфраструктура</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>Многоразовые шаблоны Remotion, локальный рендер, тестирование и небольшой резерв на рендер/облако для регулярных публичных форм исследования.</x:v>
+        <x:v>Многоразовые шаблоны Remotion, локальный рендер, тестирование и небольшой резерв на рендер/облако.</x:v>
       </x:c>
       <x:c r="C7" s="28" t="n">
         <x:v>600</x:v>
@@ -934,7 +913,7 @@
         <x:v>Оборудование / рабочая станция</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>Мощный ноутбук/рабочая станция, широкий монитор, внешний SSD/резервный диск, хаб/периферия для редактирования, публикации и работы с многоязычным архивом.</x:v>
+        <x:v>Мощный ноутбук/рабочая станция, широкий монитор, внешний SSD/резервный диск, хаб/периферия для видео и публикаций.</x:v>
       </x:c>
       <x:c r="C8" s="28" t="n">
         <x:v>6000</x:v>
@@ -949,7 +928,7 @@
         <x:v>Интернет, резервное копирование и технический резерв</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>Стабильное подключение, мобильный/дорожный интернет-резерв, бэкапы, запас хранилища и техническая непрерывность для сохранения архива и рабочих материалов.</x:v>
+        <x:v>Стабильное подключение, мобильный/дорожный интернет-резерв, бэкапы, запас хранилища и техническая непрерывность.</x:v>
       </x:c>
       <x:c r="C9" s="28" t="n">
         <x:v>2000</x:v>
@@ -1010,7 +989,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06b614c014f044dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra68451b53d2644ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1209,7 +1188,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>Допущения по озвучке, видео и многоязычному производству публичных форм исследования</x:v>
+        <x:v>Допущения по озвучке, видео и многоязычному производству</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str"/>
       <x:c r="C2" s="11" t="str"/>
@@ -1265,7 +1244,7 @@
       <x:c r="A8" s="11" t="str">
         <x:v>Минут озвучки больших роликов в месяц</x:v>
       </x:c>
-      <x:c r="B8" s="75" t="n">
+      <x:c r="B8" s="68" t="n">
         <x:f>B5*B6*B7</x:f>
         <x:v>1890</x:v>
       </x:c>
@@ -1277,7 +1256,7 @@
       <x:c r="A9" s="11" t="str">
         <x:v>Shorts Saint Whine в месяц</x:v>
       </x:c>
-      <x:c r="B9" s="75" t="n">
+      <x:c r="B9" s="68" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
@@ -1288,7 +1267,7 @@
       <x:c r="A10" s="11" t="str">
         <x:v>Средняя длительность Short (минуты)</x:v>
       </x:c>
-      <x:c r="B10" s="75" t="n">
+      <x:c r="B10" s="68" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
@@ -1299,7 +1278,7 @@
       <x:c r="A11" s="11" t="str">
         <x:v>Языков для Shorts в базовом сценарии</x:v>
       </x:c>
-      <x:c r="B11" s="75" t="n">
+      <x:c r="B11" s="68" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
@@ -1310,7 +1289,7 @@
       <x:c r="A12" s="11" t="str">
         <x:v>Минут озвучки Shorts в месяц</x:v>
       </x:c>
-      <x:c r="B12" s="75" t="n">
+      <x:c r="B12" s="68" t="n">
         <x:f>B9*B10*B11</x:f>
         <x:v>30</x:v>
       </x:c>
@@ -1322,7 +1301,7 @@
       <x:c r="A13" s="11" t="str">
         <x:v>Резерв на перегенерации и тесты</x:v>
       </x:c>
-      <x:c r="B13" s="76" t="n">
+      <x:c r="B13" s="69" t="n">
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
@@ -1333,19 +1312,19 @@
       <x:c r="A14" s="11" t="str">
         <x:v>Оценка минут озвучки с резервом</x:v>
       </x:c>
-      <x:c r="B14" s="75" t="n">
+      <x:c r="B14" s="69" t="n">
         <x:f>(B8+B12)*(1+B13)</x:f>
         <x:v>2304</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>(1 890 + 30) × 1,2 = 2 304 минут/месяц</x:v>
+        <x:v>Большие ролики + Shorts + 20% резерв</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
         <x:v>Примерная месячная ёмкость ElevenLabs Business</x:v>
       </x:c>
-      <x:c r="B15" s="75" t="n">
+      <x:c r="B15" s="69" t="n">
         <x:v>6000</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
@@ -1356,34 +1335,13 @@
       <x:c r="A16" s="11" t="str">
         <x:v>Оценка запаса месячной ёмкости</x:v>
       </x:c>
-      <x:c r="B16" s="75" t="n">
+      <x:c r="B16" s="69" t="n">
         <x:f>B15-B14</x:f>
         <x:v>3696</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
         <x:v>Примерный запас на тесты, дополнительные Shorts и рост</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="74" t="str">
-        <x:v>Иерархия бюджета</x:v>
-      </x:c>
-      <x:c r="B18" s="74"/>
-      <x:c r="C18" s="74"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="11" t="str">
-        <x:v>способ видеть → исследование смысла → формы фиксации → публичная платформа → производственная инфраструктура</x:v>
-      </x:c>
-      <x:c r="B19" s="11"/>
-      <x:c r="C19" s="11"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="11" t="str">
-        <x:v>Инфраструктура является рабочей базой для сохранения, перевода и передачи исследования в литературных, аудио-, видео- и многоязычных форматах.</x:v>
-      </x:c>
-      <x:c r="B20" s="11"/>
-      <x:c r="C20" s="11"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
